--- a/public/downloads/cash-flow-forecast.xlsx
+++ b/public/downloads/cash-flow-forecast.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Explore Excel\Explore Excel Updated\explore-excel-complete\explore-excel\public\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F8D95A-C72F-4D9F-87BC-5A5FF8B8BA72}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBCECBE-406B-4419-8F9C-EE6035B6C244}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,18 +422,6 @@
   </cellStyleXfs>
   <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -466,6 +454,18 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -794,1281 +794,1281 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="A1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="str">
+      <c r="C4" s="2" t="str">
         <f>Assumptions!B4</f>
         <v>2026-01-05</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="3">
         <f>Assumptions!B5</f>
         <v>45000</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="3">
         <f>Assumptions!B6</f>
         <v>20000</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="5">
         <f>$C$4+0</f>
         <v>46027</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="5">
         <f>$C$4+7</f>
         <v>46034</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="5">
         <f>$C$4+14</f>
         <v>46041</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="5">
         <f>$C$4+21</f>
         <v>46048</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="5">
         <f>$C$4+28</f>
         <v>46055</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="5">
         <f>$C$4+35</f>
         <v>46062</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="5">
         <f>$C$4+42</f>
         <v>46069</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="5">
         <f>$C$4+49</f>
         <v>46076</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="5">
         <f>$C$4+56</f>
         <v>46083</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="5">
         <f>$C$4+63</f>
         <v>46090</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="5">
         <f>$C$4+70</f>
         <v>46097</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="5">
         <f>$C$4+77</f>
         <v>46104</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="5">
         <f>$C$4+84</f>
         <v>46111</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="13">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13">
-        <v>0</v>
-      </c>
-      <c r="E10" s="13">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
-        <v>0</v>
-      </c>
-      <c r="I10" s="13">
-        <v>0</v>
-      </c>
-      <c r="J10" s="13">
-        <v>0</v>
-      </c>
-      <c r="K10" s="13">
-        <v>0</v>
-      </c>
-      <c r="L10" s="13">
-        <v>0</v>
-      </c>
-      <c r="M10" s="13">
-        <v>0</v>
-      </c>
-      <c r="N10" s="13">
-        <v>0</v>
-      </c>
-      <c r="O10" s="13">
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+      <c r="O10" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="13">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13">
-        <v>0</v>
-      </c>
-      <c r="E11" s="13">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13">
-        <v>0</v>
-      </c>
-      <c r="J11" s="13">
-        <v>0</v>
-      </c>
-      <c r="K11" s="13">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0</v>
-      </c>
-      <c r="M11" s="13">
-        <v>0</v>
-      </c>
-      <c r="N11" s="13">
-        <v>0</v>
-      </c>
-      <c r="O11" s="13">
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0</v>
+      </c>
+      <c r="O11" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="13">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13">
-        <v>0</v>
-      </c>
-      <c r="E12" s="13">
-        <v>0</v>
-      </c>
-      <c r="F12" s="13">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
-        <v>0</v>
-      </c>
-      <c r="I12" s="13">
-        <v>0</v>
-      </c>
-      <c r="J12" s="13">
-        <v>0</v>
-      </c>
-      <c r="K12" s="13">
-        <v>0</v>
-      </c>
-      <c r="L12" s="13">
-        <v>0</v>
-      </c>
-      <c r="M12" s="13">
-        <v>0</v>
-      </c>
-      <c r="N12" s="13">
-        <v>0</v>
-      </c>
-      <c r="O12" s="13">
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="13">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13">
-        <v>0</v>
-      </c>
-      <c r="E13" s="13">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13">
-        <v>0</v>
-      </c>
-      <c r="I13" s="13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="13">
-        <v>0</v>
-      </c>
-      <c r="L13" s="13">
-        <v>0</v>
-      </c>
-      <c r="M13" s="13">
-        <v>0</v>
-      </c>
-      <c r="N13" s="13">
-        <v>0</v>
-      </c>
-      <c r="O13" s="13">
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9">
+        <v>0</v>
+      </c>
+      <c r="O13" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="13">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13">
-        <v>0</v>
-      </c>
-      <c r="E14" s="13">
-        <v>0</v>
-      </c>
-      <c r="F14" s="13">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13">
-        <v>0</v>
-      </c>
-      <c r="J14" s="13">
-        <v>0</v>
-      </c>
-      <c r="K14" s="13">
-        <v>0</v>
-      </c>
-      <c r="L14" s="13">
-        <v>0</v>
-      </c>
-      <c r="M14" s="13">
-        <v>0</v>
-      </c>
-      <c r="N14" s="13">
-        <v>0</v>
-      </c>
-      <c r="O14" s="13">
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+      <c r="O14" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="15">
+      <c r="B15" s="7"/>
+      <c r="C15" s="11">
         <f t="shared" ref="C15:O15" si="0">SUM(C10:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K15" s="15">
+      <c r="K15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O15" s="15">
+      <c r="O15" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="13">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13">
-        <v>0</v>
-      </c>
-      <c r="E18" s="13">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13">
-        <v>0</v>
-      </c>
-      <c r="G18" s="13">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13">
-        <v>0</v>
-      </c>
-      <c r="I18" s="13">
-        <v>0</v>
-      </c>
-      <c r="J18" s="13">
-        <v>0</v>
-      </c>
-      <c r="K18" s="13">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13">
-        <v>0</v>
-      </c>
-      <c r="M18" s="13">
-        <v>0</v>
-      </c>
-      <c r="N18" s="13">
-        <v>0</v>
-      </c>
-      <c r="O18" s="13">
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+      <c r="O18" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="13">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0</v>
-      </c>
-      <c r="G19" s="13">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13">
-        <v>0</v>
-      </c>
-      <c r="I19" s="13">
-        <v>0</v>
-      </c>
-      <c r="J19" s="13">
-        <v>0</v>
-      </c>
-      <c r="K19" s="13">
-        <v>0</v>
-      </c>
-      <c r="L19" s="13">
-        <v>0</v>
-      </c>
-      <c r="M19" s="13">
-        <v>0</v>
-      </c>
-      <c r="N19" s="13">
-        <v>0</v>
-      </c>
-      <c r="O19" s="13">
+      <c r="C19" s="9">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>0</v>
+      </c>
+      <c r="I19" s="9">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="13">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13">
-        <v>0</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13">
-        <v>0</v>
-      </c>
-      <c r="G20" s="13">
-        <v>0</v>
-      </c>
-      <c r="H20" s="13">
-        <v>0</v>
-      </c>
-      <c r="I20" s="13">
-        <v>0</v>
-      </c>
-      <c r="J20" s="13">
-        <v>0</v>
-      </c>
-      <c r="K20" s="13">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13">
-        <v>0</v>
-      </c>
-      <c r="M20" s="13">
-        <v>0</v>
-      </c>
-      <c r="N20" s="13">
-        <v>0</v>
-      </c>
-      <c r="O20" s="13">
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+      <c r="O20" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="13">
-        <v>0</v>
-      </c>
-      <c r="D21" s="13">
-        <v>0</v>
-      </c>
-      <c r="E21" s="13">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13">
-        <v>0</v>
-      </c>
-      <c r="G21" s="13">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13">
-        <v>0</v>
-      </c>
-      <c r="I21" s="13">
-        <v>0</v>
-      </c>
-      <c r="J21" s="13">
-        <v>0</v>
-      </c>
-      <c r="K21" s="13">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13">
-        <v>0</v>
-      </c>
-      <c r="M21" s="13">
-        <v>0</v>
-      </c>
-      <c r="N21" s="13">
-        <v>0</v>
-      </c>
-      <c r="O21" s="13">
+      <c r="C21" s="9">
+        <v>0</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
+      <c r="O21" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="13">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13">
-        <v>0</v>
-      </c>
-      <c r="E22" s="13">
-        <v>0</v>
-      </c>
-      <c r="F22" s="13">
-        <v>0</v>
-      </c>
-      <c r="G22" s="13">
-        <v>0</v>
-      </c>
-      <c r="H22" s="13">
-        <v>0</v>
-      </c>
-      <c r="I22" s="13">
-        <v>0</v>
-      </c>
-      <c r="J22" s="13">
-        <v>0</v>
-      </c>
-      <c r="K22" s="13">
-        <v>0</v>
-      </c>
-      <c r="L22" s="13">
-        <v>0</v>
-      </c>
-      <c r="M22" s="13">
-        <v>0</v>
-      </c>
-      <c r="N22" s="13">
-        <v>0</v>
-      </c>
-      <c r="O22" s="13">
+      <c r="C22" s="9">
+        <v>0</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9">
+        <v>0</v>
+      </c>
+      <c r="O22" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="13">
-        <v>0</v>
-      </c>
-      <c r="D23" s="13">
-        <v>0</v>
-      </c>
-      <c r="E23" s="13">
-        <v>0</v>
-      </c>
-      <c r="F23" s="13">
-        <v>0</v>
-      </c>
-      <c r="G23" s="13">
-        <v>0</v>
-      </c>
-      <c r="H23" s="13">
-        <v>0</v>
-      </c>
-      <c r="I23" s="13">
-        <v>0</v>
-      </c>
-      <c r="J23" s="13">
-        <v>0</v>
-      </c>
-      <c r="K23" s="13">
-        <v>0</v>
-      </c>
-      <c r="L23" s="13">
-        <v>0</v>
-      </c>
-      <c r="M23" s="13">
-        <v>0</v>
-      </c>
-      <c r="N23" s="13">
-        <v>0</v>
-      </c>
-      <c r="O23" s="13">
+      <c r="C23" s="9">
+        <v>0</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>0</v>
+      </c>
+      <c r="I23" s="9">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9">
+        <v>0</v>
+      </c>
+      <c r="O23" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="13">
-        <v>0</v>
-      </c>
-      <c r="D24" s="13">
-        <v>0</v>
-      </c>
-      <c r="E24" s="13">
-        <v>0</v>
-      </c>
-      <c r="F24" s="13">
-        <v>0</v>
-      </c>
-      <c r="G24" s="13">
-        <v>0</v>
-      </c>
-      <c r="H24" s="13">
-        <v>0</v>
-      </c>
-      <c r="I24" s="13">
-        <v>0</v>
-      </c>
-      <c r="J24" s="13">
-        <v>0</v>
-      </c>
-      <c r="K24" s="13">
-        <v>0</v>
-      </c>
-      <c r="L24" s="13">
-        <v>0</v>
-      </c>
-      <c r="M24" s="13">
-        <v>0</v>
-      </c>
-      <c r="N24" s="13">
-        <v>0</v>
-      </c>
-      <c r="O24" s="13">
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>0</v>
+      </c>
+      <c r="I24" s="9">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9">
+        <v>0</v>
+      </c>
+      <c r="O24" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="13">
-        <v>0</v>
-      </c>
-      <c r="D25" s="13">
-        <v>0</v>
-      </c>
-      <c r="E25" s="13">
-        <v>0</v>
-      </c>
-      <c r="F25" s="13">
-        <v>0</v>
-      </c>
-      <c r="G25" s="13">
-        <v>0</v>
-      </c>
-      <c r="H25" s="13">
-        <v>0</v>
-      </c>
-      <c r="I25" s="13">
-        <v>0</v>
-      </c>
-      <c r="J25" s="13">
-        <v>0</v>
-      </c>
-      <c r="K25" s="13">
-        <v>0</v>
-      </c>
-      <c r="L25" s="13">
-        <v>0</v>
-      </c>
-      <c r="M25" s="13">
-        <v>0</v>
-      </c>
-      <c r="N25" s="13">
-        <v>0</v>
-      </c>
-      <c r="O25" s="13">
+      <c r="C25" s="9">
+        <v>0</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>0</v>
+      </c>
+      <c r="I25" s="9">
+        <v>0</v>
+      </c>
+      <c r="J25" s="9">
+        <v>0</v>
+      </c>
+      <c r="K25" s="9">
+        <v>0</v>
+      </c>
+      <c r="L25" s="9">
+        <v>0</v>
+      </c>
+      <c r="M25" s="9">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9">
+        <v>0</v>
+      </c>
+      <c r="O25" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="13">
-        <v>0</v>
-      </c>
-      <c r="D26" s="13">
-        <v>0</v>
-      </c>
-      <c r="E26" s="13">
-        <v>0</v>
-      </c>
-      <c r="F26" s="13">
-        <v>0</v>
-      </c>
-      <c r="G26" s="13">
-        <v>0</v>
-      </c>
-      <c r="H26" s="13">
-        <v>0</v>
-      </c>
-      <c r="I26" s="13">
-        <v>0</v>
-      </c>
-      <c r="J26" s="13">
-        <v>0</v>
-      </c>
-      <c r="K26" s="13">
-        <v>0</v>
-      </c>
-      <c r="L26" s="13">
-        <v>0</v>
-      </c>
-      <c r="M26" s="13">
-        <v>0</v>
-      </c>
-      <c r="N26" s="13">
-        <v>0</v>
-      </c>
-      <c r="O26" s="13">
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9">
+        <v>0</v>
+      </c>
+      <c r="M26" s="9">
+        <v>0</v>
+      </c>
+      <c r="N26" s="9">
+        <v>0</v>
+      </c>
+      <c r="O26" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="15">
+      <c r="B27" s="7"/>
+      <c r="C27" s="11">
         <f t="shared" ref="C27:O27" si="1">SUM(C18:C26)</f>
         <v>0</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="15">
+      <c r="K27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M27" s="15">
+      <c r="M27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N27" s="15">
+      <c r="N27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O27" s="15">
+      <c r="O27" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="13">
         <f>$C$5</f>
         <v>45000</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="13">
         <f t="shared" ref="D30:O30" si="2">C33</f>
         <v>45000</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="K30" s="17">
+      <c r="K30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="L30" s="17">
+      <c r="L30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="M30" s="17">
+      <c r="M30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="N30" s="17">
+      <c r="N30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
-      <c r="O30" s="17">
+      <c r="O30" s="13">
         <f t="shared" si="2"/>
         <v>45000</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="13">
         <f t="shared" ref="C31:O31" si="3">C15-C27</f>
         <v>0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="17">
+      <c r="J31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K31" s="17">
+      <c r="K31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L31" s="17">
+      <c r="L31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M31" s="17">
+      <c r="M31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N31" s="17">
+      <c r="N31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O31" s="17">
+      <c r="O31" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="12"/>
+      <c r="A32" s="8"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="15">
+      <c r="B33" s="7"/>
+      <c r="C33" s="11">
         <f t="shared" ref="C33:O33" si="4">C30+C31</f>
         <v>45000</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="E33" s="15">
+      <c r="E33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="H33" s="15">
+      <c r="H33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="L33" s="15">
+      <c r="L33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="M33" s="15">
+      <c r="M33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="N33" s="15">
+      <c r="N33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
-      <c r="O33" s="15">
+      <c r="O33" s="11">
         <f t="shared" si="4"/>
         <v>45000</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="13">
         <f t="shared" ref="C34:O34" si="5">C33-$C$6</f>
         <v>25000</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="I34" s="17">
+      <c r="I34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="J34" s="17">
+      <c r="J34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="K34" s="17">
+      <c r="K34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="L34" s="17">
+      <c r="L34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="M34" s="17">
+      <c r="M34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
-      <c r="O34" s="17">
+      <c r="O34" s="13">
         <f t="shared" si="5"/>
         <v>25000</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C36" s="18" t="str">
+      <c r="C36" s="14" t="str">
         <f t="shared" ref="C36:O36" si="6">IF(C33&lt;$C$6,"CHECK","")</f>
         <v/>
       </c>
-      <c r="D36" s="18" t="str">
+      <c r="D36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="E36" s="18" t="str">
+      <c r="E36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="F36" s="18" t="str">
+      <c r="F36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G36" s="18" t="str">
+      <c r="G36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="H36" s="18" t="str">
+      <c r="H36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="I36" s="18" t="str">
+      <c r="I36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="J36" s="18" t="str">
+      <c r="J36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="K36" s="18" t="str">
+      <c r="K36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="L36" s="18" t="str">
+      <c r="L36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="M36" s="18" t="str">
+      <c r="M36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="N36" s="18" t="str">
+      <c r="N36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O36" s="18" t="str">
+      <c r="O36" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="16" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="20" t="s">
+      <c r="A40" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="16" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="16" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="17" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2103,112 +2103,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="23">
-        <v>45000</v>
-      </c>
-      <c r="C5" s="21" t="s">
+      <c r="B5" s="19">
+        <v>45000</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="19">
         <v>20000</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="17" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="20">
         <v>0.6</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="17" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="20">
         <v>0.3</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="17" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="20">
         <v>0.08</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="20">
         <v>0.02</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="22">
         <f>SUM(B9:B12)</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="17" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2240,307 +2240,307 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="23" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="28">
+      <c r="A5" s="24">
         <f>Forecast!C$8</f>
         <v>46027</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="13">
         <f>Forecast!C$33</f>
         <v>45000</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="17" t="str">
+      <c r="C5" s="19"/>
+      <c r="D5" s="13" t="str">
         <f t="shared" ref="D5:D17" si="0">IF(C5="","",C5-B5)</f>
         <v/>
       </c>
-      <c r="E5" s="29" t="str">
+      <c r="E5" s="25" t="str">
         <f t="shared" ref="E5:E17" si="1">IF(OR(C5="",B5=0),"",D5/ABS(B5))</f>
         <v/>
       </c>
-      <c r="F5" s="30"/>
+      <c r="F5" s="26"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="28">
+      <c r="A6" s="24">
         <f>Forecast!D$8</f>
         <v>46034</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="13">
         <f>Forecast!D$33</f>
         <v>45000</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="17" t="str">
+      <c r="C6" s="19"/>
+      <c r="D6" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E6" s="29" t="str">
+      <c r="E6" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F6" s="30"/>
+      <c r="F6" s="26"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="28">
+      <c r="A7" s="24">
         <f>Forecast!E$8</f>
         <v>46041</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="13">
         <f>Forecast!E$33</f>
         <v>45000</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="17" t="str">
+      <c r="C7" s="19"/>
+      <c r="D7" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E7" s="29" t="str">
+      <c r="E7" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F7" s="30"/>
+      <c r="F7" s="26"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="28">
+      <c r="A8" s="24">
         <f>Forecast!F$8</f>
         <v>46048</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="13">
         <f>Forecast!F$33</f>
         <v>45000</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="17" t="str">
+      <c r="C8" s="19"/>
+      <c r="D8" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E8" s="29" t="str">
+      <c r="E8" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F8" s="30"/>
+      <c r="F8" s="26"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="28">
+      <c r="A9" s="24">
         <f>Forecast!G$8</f>
         <v>46055</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="13">
         <f>Forecast!G$33</f>
         <v>45000</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="17" t="str">
+      <c r="C9" s="19"/>
+      <c r="D9" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E9" s="29" t="str">
+      <c r="E9" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F9" s="30"/>
+      <c r="F9" s="26"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="28">
+      <c r="A10" s="24">
         <f>Forecast!H$8</f>
         <v>46062</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="13">
         <f>Forecast!H$33</f>
         <v>45000</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="17" t="str">
+      <c r="C10" s="19"/>
+      <c r="D10" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E10" s="29" t="str">
+      <c r="E10" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F10" s="30"/>
+      <c r="F10" s="26"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="28">
+      <c r="A11" s="24">
         <f>Forecast!I$8</f>
         <v>46069</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="13">
         <f>Forecast!I$33</f>
         <v>45000</v>
       </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="17" t="str">
+      <c r="C11" s="19"/>
+      <c r="D11" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E11" s="29" t="str">
+      <c r="E11" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F11" s="30"/>
+      <c r="F11" s="26"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="28">
+      <c r="A12" s="24">
         <f>Forecast!J$8</f>
         <v>46076</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="13">
         <f>Forecast!J$33</f>
         <v>45000</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="17" t="str">
+      <c r="C12" s="19"/>
+      <c r="D12" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E12" s="29" t="str">
+      <c r="E12" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F12" s="30"/>
+      <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="28">
+      <c r="A13" s="24">
         <f>Forecast!K$8</f>
         <v>46083</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="13">
         <f>Forecast!K$33</f>
         <v>45000</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="17" t="str">
+      <c r="C13" s="19"/>
+      <c r="D13" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E13" s="29" t="str">
+      <c r="E13" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F13" s="30"/>
+      <c r="F13" s="26"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="28">
+      <c r="A14" s="24">
         <f>Forecast!L$8</f>
         <v>46090</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="13">
         <f>Forecast!L$33</f>
         <v>45000</v>
       </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="17" t="str">
+      <c r="C14" s="19"/>
+      <c r="D14" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E14" s="29" t="str">
+      <c r="E14" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F14" s="30"/>
+      <c r="F14" s="26"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="28">
+      <c r="A15" s="24">
         <f>Forecast!M$8</f>
         <v>46097</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="13">
         <f>Forecast!M$33</f>
         <v>45000</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="17" t="str">
+      <c r="C15" s="19"/>
+      <c r="D15" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E15" s="29" t="str">
+      <c r="E15" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F15" s="30"/>
+      <c r="F15" s="26"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="28">
+      <c r="A16" s="24">
         <f>Forecast!N$8</f>
         <v>46104</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="13">
         <f>Forecast!N$33</f>
         <v>45000</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="17" t="str">
+      <c r="C16" s="19"/>
+      <c r="D16" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E16" s="29" t="str">
+      <c r="E16" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F16" s="30"/>
+      <c r="F16" s="26"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="28">
+      <c r="A17" s="24">
         <f>Forecast!O$8</f>
         <v>46111</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="13">
         <f>Forecast!O$33</f>
         <v>45000</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="17" t="str">
+      <c r="C17" s="19"/>
+      <c r="D17" s="13" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E17" s="29" t="str">
+      <c r="E17" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F17" s="30"/>
+      <c r="F17" s="26"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="17" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2569,135 +2569,135 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+    </row>
+    <row r="19" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+    </row>
+    <row r="22" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
